--- a/experiment/SwinT2_bestx4/Test/results-Urban100/Urban100.xlsx
+++ b/experiment/SwinT2_bestx4/Test/results-Urban100/Urban100.xlsx
@@ -452,10 +452,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>27.37</v>
+        <v>27.39</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7586000000000001</v>
+        <v>0.7594</v>
       </c>
     </row>
     <row r="3">
@@ -465,10 +465,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>26.34</v>
+        <v>26.39</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8006</v>
+        <v>0.8027</v>
       </c>
     </row>
     <row r="4">
@@ -478,10 +478,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23.72</v>
+        <v>23.75</v>
       </c>
       <c r="C4" t="n">
-        <v>0.676</v>
+        <v>0.6787</v>
       </c>
     </row>
     <row r="5">
@@ -491,10 +491,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22.89</v>
+        <v>22.83</v>
       </c>
       <c r="C5" t="n">
-        <v>0.8112</v>
+        <v>0.8095</v>
       </c>
     </row>
     <row r="6">
@@ -504,10 +504,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>27.18</v>
+        <v>27.3</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9372</v>
+        <v>0.9392</v>
       </c>
     </row>
     <row r="7">
@@ -517,10 +517,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22.27</v>
+        <v>22.29</v>
       </c>
       <c r="C7" t="n">
-        <v>0.6176</v>
+        <v>0.6188</v>
       </c>
     </row>
     <row r="8">
@@ -530,10 +530,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29.31</v>
+        <v>29.33</v>
       </c>
       <c r="C8" t="n">
-        <v>0.8559</v>
+        <v>0.8567</v>
       </c>
     </row>
     <row r="9">
@@ -543,10 +543,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21.27</v>
+        <v>21.28</v>
       </c>
       <c r="C9" t="n">
-        <v>0.6434</v>
+        <v>0.6468</v>
       </c>
     </row>
     <row r="10">
@@ -556,10 +556,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>33.07</v>
+        <v>33.28</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9132</v>
+        <v>0.9159</v>
       </c>
     </row>
     <row r="11">
@@ -569,10 +569,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>26.61</v>
+        <v>26.66</v>
       </c>
       <c r="C11" t="n">
-        <v>0.8744</v>
+        <v>0.876</v>
       </c>
     </row>
     <row r="12">
@@ -582,10 +582,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18.03</v>
+        <v>18.55</v>
       </c>
       <c r="C12" t="n">
-        <v>0.7886</v>
+        <v>0.8053</v>
       </c>
     </row>
     <row r="13">
@@ -595,10 +595,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23.77</v>
+        <v>23.79</v>
       </c>
       <c r="C13" t="n">
-        <v>0.7214</v>
+        <v>0.7229</v>
       </c>
     </row>
     <row r="14">
@@ -608,10 +608,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29.24</v>
+        <v>29.28</v>
       </c>
       <c r="C14" t="n">
-        <v>0.8280999999999999</v>
+        <v>0.8295</v>
       </c>
     </row>
     <row r="15">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22.28</v>
+        <v>22.29</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6742</v>
+        <v>0.6765</v>
       </c>
     </row>
     <row r="16">
@@ -634,10 +634,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>25.88</v>
+        <v>25.94</v>
       </c>
       <c r="C16" t="n">
-        <v>0.7279</v>
+        <v>0.7294</v>
       </c>
     </row>
     <row r="17">
@@ -647,10 +647,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29.51</v>
+        <v>29.65</v>
       </c>
       <c r="C17" t="n">
-        <v>0.9048</v>
+        <v>0.9064</v>
       </c>
     </row>
     <row r="18">
@@ -660,10 +660,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>25.44</v>
+        <v>25.51</v>
       </c>
       <c r="C18" t="n">
-        <v>0.8163</v>
+        <v>0.8186</v>
       </c>
     </row>
     <row r="19">
@@ -673,10 +673,10 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>26.31</v>
+        <v>26.32</v>
       </c>
       <c r="C19" t="n">
-        <v>0.7097</v>
+        <v>0.7106</v>
       </c>
     </row>
     <row r="20">
@@ -686,10 +686,10 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>21.77</v>
+        <v>21.82</v>
       </c>
       <c r="C20" t="n">
-        <v>0.8015</v>
+        <v>0.8033</v>
       </c>
     </row>
     <row r="21">
@@ -699,10 +699,10 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>22.04</v>
+        <v>22.05</v>
       </c>
       <c r="C21" t="n">
-        <v>0.71</v>
+        <v>0.711</v>
       </c>
     </row>
     <row r="22">
@@ -715,7 +715,7 @@
         <v>29.55</v>
       </c>
       <c r="C22" t="n">
-        <v>0.7809</v>
+        <v>0.781</v>
       </c>
     </row>
     <row r="23">
@@ -725,10 +725,10 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>26.01</v>
+        <v>26.04</v>
       </c>
       <c r="C23" t="n">
-        <v>0.7554999999999999</v>
+        <v>0.757</v>
       </c>
     </row>
     <row r="24">
@@ -738,7 +738,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>29.86</v>
+        <v>29.87</v>
       </c>
       <c r="C24" t="n">
         <v>0.9046999999999999</v>
@@ -751,10 +751,10 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>19.73</v>
+        <v>19.81</v>
       </c>
       <c r="C25" t="n">
-        <v>0.6388</v>
+        <v>0.644</v>
       </c>
     </row>
     <row r="26">
@@ -764,10 +764,10 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>31.17</v>
+        <v>31.33</v>
       </c>
       <c r="C26" t="n">
-        <v>0.8915</v>
+        <v>0.893</v>
       </c>
     </row>
     <row r="27">
@@ -777,10 +777,10 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27.46</v>
+        <v>27.63</v>
       </c>
       <c r="C27" t="n">
-        <v>0.6862</v>
+        <v>0.6906</v>
       </c>
     </row>
     <row r="28">
@@ -790,10 +790,10 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28.08</v>
+        <v>28.1</v>
       </c>
       <c r="C28" t="n">
-        <v>0.7877</v>
+        <v>0.7886</v>
       </c>
     </row>
     <row r="29">
@@ -803,10 +803,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>31.21</v>
+        <v>31.26</v>
       </c>
       <c r="C29" t="n">
-        <v>0.8736</v>
+        <v>0.8745000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -816,10 +816,10 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>26.74</v>
+        <v>26.83</v>
       </c>
       <c r="C30" t="n">
-        <v>0.8551</v>
+        <v>0.8575</v>
       </c>
     </row>
     <row r="31">
@@ -832,7 +832,7 @@
         <v>24.18</v>
       </c>
       <c r="C31" t="n">
-        <v>0.7858000000000001</v>
+        <v>0.7864</v>
       </c>
     </row>
     <row r="32">
@@ -842,10 +842,10 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>24.13</v>
+        <v>24.17</v>
       </c>
       <c r="C32" t="n">
-        <v>0.7827</v>
+        <v>0.7845</v>
       </c>
     </row>
     <row r="33">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>28.78</v>
+        <v>28.79</v>
       </c>
       <c r="C33" t="n">
-        <v>0.8456</v>
+        <v>0.8462</v>
       </c>
     </row>
     <row r="34">
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>26.77</v>
+        <v>26.84</v>
       </c>
       <c r="C34" t="n">
-        <v>0.7851</v>
+        <v>0.7872</v>
       </c>
     </row>
     <row r="35">
@@ -881,10 +881,10 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>22.95</v>
+        <v>22.97</v>
       </c>
       <c r="C35" t="n">
-        <v>0.5805</v>
+        <v>0.5815</v>
       </c>
     </row>
     <row r="36">
@@ -894,10 +894,10 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>28.51</v>
+        <v>28.64</v>
       </c>
       <c r="C36" t="n">
-        <v>0.8631</v>
+        <v>0.8669</v>
       </c>
     </row>
     <row r="37">
@@ -907,10 +907,10 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>28.47</v>
+        <v>28.51</v>
       </c>
       <c r="C37" t="n">
-        <v>0.8787</v>
+        <v>0.8798</v>
       </c>
     </row>
     <row r="38">
@@ -920,10 +920,10 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>26.37</v>
+        <v>26.4</v>
       </c>
       <c r="C38" t="n">
-        <v>0.7955</v>
+        <v>0.797</v>
       </c>
     </row>
     <row r="39">
@@ -933,10 +933,10 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>26.83</v>
+        <v>26.89</v>
       </c>
       <c r="C39" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.6715</v>
       </c>
     </row>
     <row r="40">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>22.71</v>
+        <v>22.73</v>
       </c>
       <c r="C40" t="n">
-        <v>0.7222</v>
+        <v>0.7228</v>
       </c>
     </row>
     <row r="41">
@@ -959,10 +959,10 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>26.18</v>
+        <v>26.36</v>
       </c>
       <c r="C41" t="n">
-        <v>0.9241</v>
+        <v>0.9274</v>
       </c>
     </row>
     <row r="42">
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>25.55</v>
+        <v>25.61</v>
       </c>
       <c r="C42" t="n">
-        <v>0.8626</v>
+        <v>0.8653</v>
       </c>
     </row>
     <row r="43">
@@ -985,10 +985,10 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>28.34</v>
+        <v>28.39</v>
       </c>
       <c r="C43" t="n">
-        <v>0.8758</v>
+        <v>0.8771</v>
       </c>
     </row>
     <row r="44">
@@ -998,10 +998,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>30.86</v>
+        <v>31.11</v>
       </c>
       <c r="C44" t="n">
-        <v>0.9242</v>
+        <v>0.9261</v>
       </c>
     </row>
     <row r="45">
@@ -1011,10 +1011,10 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>31.21</v>
+        <v>31.31</v>
       </c>
       <c r="C45" t="n">
-        <v>0.8557</v>
+        <v>0.858</v>
       </c>
     </row>
     <row r="46">
@@ -1024,10 +1024,10 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>23.62</v>
+        <v>23.87</v>
       </c>
       <c r="C46" t="n">
-        <v>0.6818</v>
+        <v>0.6873</v>
       </c>
     </row>
     <row r="47">
@@ -1037,10 +1037,10 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>23.58</v>
+        <v>23.61</v>
       </c>
       <c r="C47" t="n">
-        <v>0.7534</v>
+        <v>0.7554999999999999</v>
       </c>
     </row>
     <row r="48">
@@ -1050,10 +1050,10 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>21.74</v>
+        <v>21.79</v>
       </c>
       <c r="C48" t="n">
-        <v>0.7595</v>
+        <v>0.763</v>
       </c>
     </row>
     <row r="49">
@@ -1063,10 +1063,10 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>20.01</v>
+        <v>19.99</v>
       </c>
       <c r="C49" t="n">
-        <v>0.7987</v>
+        <v>0.7983</v>
       </c>
     </row>
     <row r="50">
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>23.32</v>
+        <v>23.35</v>
       </c>
       <c r="C50" t="n">
-        <v>0.7403</v>
+        <v>0.7419</v>
       </c>
     </row>
     <row r="51">
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>25.29</v>
+        <v>25.31</v>
       </c>
       <c r="C51" t="n">
-        <v>0.7651</v>
+        <v>0.7663</v>
       </c>
     </row>
     <row r="52">
@@ -1102,10 +1102,10 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>27.1</v>
+        <v>27.14</v>
       </c>
       <c r="C52" t="n">
-        <v>0.8366</v>
+        <v>0.8383</v>
       </c>
     </row>
     <row r="53">
@@ -1118,7 +1118,7 @@
         <v>28.12</v>
       </c>
       <c r="C53" t="n">
-        <v>0.8911</v>
+        <v>0.8927</v>
       </c>
     </row>
     <row r="54">
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="B54" t="n">
-        <v>22.16</v>
+        <v>22.19</v>
       </c>
       <c r="C54" t="n">
-        <v>0.716</v>
+        <v>0.7178</v>
       </c>
     </row>
     <row r="55">
@@ -1141,10 +1141,10 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>21</v>
+        <v>21.04</v>
       </c>
       <c r="C55" t="n">
-        <v>0.6352</v>
+        <v>0.6383</v>
       </c>
     </row>
     <row r="56">
@@ -1154,7 +1154,7 @@
         </is>
       </c>
       <c r="B56" t="n">
-        <v>32.36</v>
+        <v>32.43</v>
       </c>
       <c r="C56" t="n">
         <v>0.9369</v>
@@ -1167,10 +1167,10 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>24.55</v>
+        <v>24.61</v>
       </c>
       <c r="C57" t="n">
-        <v>0.7651</v>
+        <v>0.768</v>
       </c>
     </row>
     <row r="58">
@@ -1180,10 +1180,10 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>30.29</v>
+        <v>30.38</v>
       </c>
       <c r="C58" t="n">
-        <v>0.8781</v>
+        <v>0.8797</v>
       </c>
     </row>
     <row r="59">
@@ -1193,10 +1193,10 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>25.35</v>
+        <v>25.42</v>
       </c>
       <c r="C59" t="n">
-        <v>0.8445</v>
+        <v>0.8469</v>
       </c>
     </row>
     <row r="60">
@@ -1206,10 +1206,10 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>21.78</v>
+        <v>21.88</v>
       </c>
       <c r="C60" t="n">
-        <v>0.7484</v>
+        <v>0.7532</v>
       </c>
     </row>
     <row r="61">
@@ -1219,10 +1219,10 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>22.4</v>
+        <v>22.42</v>
       </c>
       <c r="C61" t="n">
-        <v>0.5561</v>
+        <v>0.5582</v>
       </c>
     </row>
     <row r="62">
@@ -1232,10 +1232,10 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>24.4</v>
+        <v>24.39</v>
       </c>
       <c r="C62" t="n">
-        <v>0.7389</v>
+        <v>0.739</v>
       </c>
     </row>
     <row r="63">
@@ -1245,10 +1245,10 @@
         </is>
       </c>
       <c r="B63" t="n">
-        <v>21.57</v>
+        <v>21.53</v>
       </c>
       <c r="C63" t="n">
-        <v>0.7904</v>
+        <v>0.7916</v>
       </c>
     </row>
     <row r="64">
@@ -1258,10 +1258,10 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>22.1</v>
+        <v>22.14</v>
       </c>
       <c r="C64" t="n">
-        <v>0.6106</v>
+        <v>0.6116</v>
       </c>
     </row>
     <row r="65">
@@ -1271,10 +1271,10 @@
         </is>
       </c>
       <c r="B65" t="n">
-        <v>26.39</v>
+        <v>26.41</v>
       </c>
       <c r="C65" t="n">
-        <v>0.7763</v>
+        <v>0.7768</v>
       </c>
     </row>
     <row r="66">
@@ -1284,10 +1284,10 @@
         </is>
       </c>
       <c r="B66" t="n">
-        <v>25.18</v>
+        <v>25.19</v>
       </c>
       <c r="C66" t="n">
-        <v>0.7085</v>
+        <v>0.7094</v>
       </c>
     </row>
     <row r="67">
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="B67" t="n">
-        <v>22.12</v>
+        <v>22.11</v>
       </c>
       <c r="C67" t="n">
-        <v>0.6345</v>
+        <v>0.6344</v>
       </c>
     </row>
     <row r="68">
@@ -1310,10 +1310,10 @@
         </is>
       </c>
       <c r="B68" t="n">
-        <v>19.42</v>
+        <v>19.32</v>
       </c>
       <c r="C68" t="n">
-        <v>0.8637</v>
+        <v>0.8643</v>
       </c>
     </row>
     <row r="69">
@@ -1323,10 +1323,10 @@
         </is>
       </c>
       <c r="B69" t="n">
-        <v>29.91</v>
+        <v>29.93</v>
       </c>
       <c r="C69" t="n">
-        <v>0.871</v>
+        <v>0.8721</v>
       </c>
     </row>
     <row r="70">
@@ -1336,10 +1336,10 @@
         </is>
       </c>
       <c r="B70" t="n">
-        <v>24.57</v>
+        <v>24.59</v>
       </c>
       <c r="C70" t="n">
-        <v>0.7403999999999999</v>
+        <v>0.742</v>
       </c>
     </row>
     <row r="71">
@@ -1349,10 +1349,10 @@
         </is>
       </c>
       <c r="B71" t="n">
-        <v>22.12</v>
+        <v>22.13</v>
       </c>
       <c r="C71" t="n">
-        <v>0.5903</v>
+        <v>0.5911</v>
       </c>
     </row>
     <row r="72">
@@ -1362,10 +1362,10 @@
         </is>
       </c>
       <c r="B72" t="n">
-        <v>27.8</v>
+        <v>27.88</v>
       </c>
       <c r="C72" t="n">
-        <v>0.6574</v>
+        <v>0.6613</v>
       </c>
     </row>
     <row r="73">
@@ -1378,7 +1378,7 @@
         <v>19.65</v>
       </c>
       <c r="C73" t="n">
-        <v>0.7943</v>
+        <v>0.7961</v>
       </c>
     </row>
     <row r="74">
@@ -1388,10 +1388,10 @@
         </is>
       </c>
       <c r="B74" t="n">
-        <v>20.08</v>
+        <v>20</v>
       </c>
       <c r="C74" t="n">
-        <v>0.5522</v>
+        <v>0.5505</v>
       </c>
     </row>
     <row r="75">
@@ -1401,10 +1401,10 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>23.55</v>
+        <v>23.62</v>
       </c>
       <c r="C75" t="n">
-        <v>0.6865</v>
+        <v>0.6899</v>
       </c>
     </row>
     <row r="76">
@@ -1414,10 +1414,10 @@
         </is>
       </c>
       <c r="B76" t="n">
-        <v>31.04</v>
+        <v>31.13</v>
       </c>
       <c r="C76" t="n">
-        <v>0.8762</v>
+        <v>0.8778</v>
       </c>
     </row>
     <row r="77">
@@ -1427,10 +1427,10 @@
         </is>
       </c>
       <c r="B77" t="n">
-        <v>22.7</v>
+        <v>22.77</v>
       </c>
       <c r="C77" t="n">
-        <v>0.7218</v>
+        <v>0.7267</v>
       </c>
     </row>
     <row r="78">
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="B78" t="n">
-        <v>22.67</v>
+        <v>22.69</v>
       </c>
       <c r="C78" t="n">
-        <v>0.669</v>
+        <v>0.6707</v>
       </c>
     </row>
     <row r="79">
@@ -1453,10 +1453,10 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>27.15</v>
+        <v>27.19</v>
       </c>
       <c r="C79" t="n">
-        <v>0.7629</v>
+        <v>0.7645999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -1466,10 +1466,10 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>25.23</v>
+        <v>25.27</v>
       </c>
       <c r="C80" t="n">
-        <v>0.6855</v>
+        <v>0.6876</v>
       </c>
     </row>
     <row r="81">
@@ -1479,10 +1479,10 @@
         </is>
       </c>
       <c r="B81" t="n">
-        <v>35.42</v>
+        <v>35.38</v>
       </c>
       <c r="C81" t="n">
-        <v>0.9494</v>
+        <v>0.9495</v>
       </c>
     </row>
     <row r="82">
@@ -1492,10 +1492,10 @@
         </is>
       </c>
       <c r="B82" t="n">
-        <v>36.52</v>
+        <v>36.6</v>
       </c>
       <c r="C82" t="n">
-        <v>0.9665</v>
+        <v>0.9671</v>
       </c>
     </row>
     <row r="83">
@@ -1505,10 +1505,10 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>32.18</v>
+        <v>32.23</v>
       </c>
       <c r="C83" t="n">
-        <v>0.9356</v>
+        <v>0.9362</v>
       </c>
     </row>
     <row r="84">
@@ -1518,10 +1518,10 @@
         </is>
       </c>
       <c r="B84" t="n">
-        <v>22.15</v>
+        <v>22.16</v>
       </c>
       <c r="C84" t="n">
-        <v>0.6885</v>
+        <v>0.6902</v>
       </c>
     </row>
     <row r="85">
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="B85" t="n">
-        <v>28.47</v>
+        <v>28.52</v>
       </c>
       <c r="C85" t="n">
-        <v>0.8033</v>
+        <v>0.8048</v>
       </c>
     </row>
     <row r="86">
@@ -1544,10 +1544,10 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>28.03</v>
+        <v>28.09</v>
       </c>
       <c r="C86" t="n">
-        <v>0.8963</v>
+        <v>0.8972</v>
       </c>
     </row>
     <row r="87">
@@ -1557,10 +1557,10 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>30.28</v>
+        <v>30.29</v>
       </c>
       <c r="C87" t="n">
-        <v>0.8826000000000001</v>
+        <v>0.8829</v>
       </c>
     </row>
     <row r="88">
@@ -1570,10 +1570,10 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>27.06</v>
+        <v>27.14</v>
       </c>
       <c r="C88" t="n">
-        <v>0.8681</v>
+        <v>0.8701</v>
       </c>
     </row>
     <row r="89">
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>19.84</v>
+        <v>19.86</v>
       </c>
       <c r="C89" t="n">
-        <v>0.5592</v>
+        <v>0.5607</v>
       </c>
     </row>
     <row r="90">
@@ -1596,10 +1596,10 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>26.65</v>
+        <v>26.68</v>
       </c>
       <c r="C90" t="n">
-        <v>0.7096</v>
+        <v>0.7122000000000001</v>
       </c>
     </row>
     <row r="91">
@@ -1609,10 +1609,10 @@
         </is>
       </c>
       <c r="B91" t="n">
-        <v>37.12</v>
+        <v>37.06</v>
       </c>
       <c r="C91" t="n">
-        <v>0.9703000000000001</v>
+        <v>0.9701</v>
       </c>
     </row>
     <row r="92">
@@ -1622,10 +1622,10 @@
         </is>
       </c>
       <c r="B92" t="n">
-        <v>23.77</v>
+        <v>23.78</v>
       </c>
       <c r="C92" t="n">
-        <v>0.6625</v>
+        <v>0.6644</v>
       </c>
     </row>
     <row r="93">
@@ -1635,10 +1635,10 @@
         </is>
       </c>
       <c r="B93" t="n">
-        <v>18.39</v>
+        <v>18.38</v>
       </c>
       <c r="C93" t="n">
-        <v>0.6182</v>
+        <v>0.6188</v>
       </c>
     </row>
     <row r="94">
@@ -1648,10 +1648,10 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>28.53</v>
+        <v>28.17</v>
       </c>
       <c r="C94" t="n">
-        <v>0.9206</v>
+        <v>0.918</v>
       </c>
     </row>
     <row r="95">
@@ -1661,10 +1661,10 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>26.96</v>
+        <v>26.98</v>
       </c>
       <c r="C95" t="n">
-        <v>0.7747000000000001</v>
+        <v>0.7755</v>
       </c>
     </row>
     <row r="96">
@@ -1674,10 +1674,10 @@
         </is>
       </c>
       <c r="B96" t="n">
-        <v>20.04</v>
+        <v>20.05</v>
       </c>
       <c r="C96" t="n">
-        <v>0.433</v>
+        <v>0.4345</v>
       </c>
     </row>
     <row r="97">
@@ -1687,10 +1687,10 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>24.55</v>
+        <v>24.57</v>
       </c>
       <c r="C97" t="n">
-        <v>0.8441</v>
+        <v>0.8456</v>
       </c>
     </row>
     <row r="98">
@@ -1700,10 +1700,10 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>24.71</v>
+        <v>24.76</v>
       </c>
       <c r="C98" t="n">
-        <v>0.7543</v>
+        <v>0.7565</v>
       </c>
     </row>
     <row r="99">
@@ -1713,10 +1713,10 @@
         </is>
       </c>
       <c r="B99" t="n">
-        <v>20.58</v>
+        <v>20.61</v>
       </c>
       <c r="C99" t="n">
-        <v>0.5172</v>
+        <v>0.5197000000000001</v>
       </c>
     </row>
     <row r="100">
@@ -1726,10 +1726,10 @@
         </is>
       </c>
       <c r="B100" t="n">
-        <v>25.25</v>
+        <v>25.43</v>
       </c>
       <c r="C100" t="n">
-        <v>0.7661</v>
+        <v>0.7746</v>
       </c>
     </row>
     <row r="101">
@@ -1739,10 +1739,10 @@
         </is>
       </c>
       <c r="B101" t="n">
-        <v>25.83</v>
+        <v>25.85</v>
       </c>
       <c r="C101" t="n">
-        <v>0.7313</v>
+        <v>0.7315</v>
       </c>
     </row>
     <row r="102">
@@ -1752,10 +1752,10 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>25.69</v>
+        <v>25.73</v>
       </c>
       <c r="C102" t="n">
-        <v>0.7718</v>
+        <v>0.7737000000000001</v>
       </c>
     </row>
   </sheetData>
